--- a/diseases/d016/2005-2009.xlsx
+++ b/diseases/d016/2005-2009.xlsx
@@ -5920,7 +5920,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17635,7 +17635,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20759,7 +20759,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22321,7 +22321,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30131,7 +30131,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31693,7 +31693,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32474,7 +32474,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33255,7 +33255,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34726,7 +34726,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -36590,7 +36590,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -38454,7 +38454,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -40548,7 +40548,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -42642,7 +42642,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -46830,7 +46830,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -48924,7 +48924,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -51018,7 +51018,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -53112,7 +53112,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -55206,7 +55206,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AJ284" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK284" t="inlineStr">
